--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,136 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>EEN0064a Spelflyktsinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123420072</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98285</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tönnebro, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605695</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6770768</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_3035</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123420072</v>
       </c>
       <c r="B3" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123420072</v>
       </c>
       <c r="B3" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123420072</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123420072</v>
       </c>
       <c r="B3" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123420072</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123420072</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>113777767</v>
       </c>
       <c r="B2" t="n">
-        <v>57181</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -811,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420072</v>
+        <v>123420070</v>
       </c>
       <c r="B3" t="n">
-        <v>98018</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605695</v>
+        <v>605715</v>
       </c>
       <c r="R3" t="n">
-        <v>6770768</v>
+        <v>6770683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_3035</t>
+          <t>2024_3037</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -900,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,6 +924,131 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123420072</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tönnebro, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>605695</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6770768</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_3035</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 53562-2024 artfynd.xlsx
+++ b/artfynd/A 53562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
           <t>EEN0064a Spelflyktsinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113777767</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420070</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,8 +1068,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>